--- a/src/test/resources/testdata/testexcelfile25.xlsx
+++ b/src/test/resources/testdata/testexcelfile25.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,19 +38,19 @@
     <t>lastName</t>
   </si>
   <si>
-    <t>gayathiri</t>
+    <t>adam</t>
   </si>
   <si>
     <t>ms</t>
   </si>
   <si>
-    <t>salehzada</t>
+    <t>belhoul</t>
   </si>
   <si>
-    <t>muse</t>
+    <t>ravika</t>
   </si>
   <si>
-    <t>canina</t>
+    <t>narine</t>
   </si>
   <si>
     <t>prachi</t>
@@ -701,7 +701,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
